--- a/artfynd/Ramsjöns naturreservat artfynd.xlsx
+++ b/artfynd/Ramsjöns naturreservat artfynd.xlsx
@@ -43144,7 +43144,7 @@
       </c>
       <c r="AC366" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Rikligt på en låga.</t>
         </is>
       </c>
       <c r="AD366" t="b">

--- a/artfynd/Ramsjöns naturreservat artfynd.xlsx
+++ b/artfynd/Ramsjöns naturreservat artfynd.xlsx
@@ -42100,7 +42100,7 @@
         <v>136880933</v>
       </c>
       <c r="B357" t="n">
-        <v>92736</v>
+        <v>92738</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>136881050</v>
       </c>
       <c r="B362" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>136880999</v>
       </c>
       <c r="B366" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>136881979</v>
       </c>
       <c r="B368" t="n">
-        <v>92787</v>
+        <v>92789</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>

--- a/artfynd/Ramsjöns naturreservat artfynd.xlsx
+++ b/artfynd/Ramsjöns naturreservat artfynd.xlsx
@@ -42100,7 +42100,7 @@
         <v>136880933</v>
       </c>
       <c r="B357" t="n">
-        <v>92738</v>
+        <v>92740</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>136881050</v>
       </c>
       <c r="B362" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>136880999</v>
       </c>
       <c r="B366" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>136881979</v>
       </c>
       <c r="B368" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>

--- a/artfynd/Ramsjöns naturreservat artfynd.xlsx
+++ b/artfynd/Ramsjöns naturreservat artfynd.xlsx
@@ -42100,7 +42100,7 @@
         <v>136880933</v>
       </c>
       <c r="B357" t="n">
-        <v>92740</v>
+        <v>92741</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>136881050</v>
       </c>
       <c r="B362" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>136880999</v>
       </c>
       <c r="B366" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>136881979</v>
       </c>
       <c r="B368" t="n">
-        <v>92791</v>
+        <v>92792</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>

--- a/artfynd/Ramsjöns naturreservat artfynd.xlsx
+++ b/artfynd/Ramsjöns naturreservat artfynd.xlsx
@@ -42100,7 +42100,7 @@
         <v>136880933</v>
       </c>
       <c r="B357" t="n">
-        <v>92741</v>
+        <v>92747</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>136881050</v>
       </c>
       <c r="B362" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>136880999</v>
       </c>
       <c r="B366" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>136881979</v>
       </c>
       <c r="B368" t="n">
-        <v>92792</v>
+        <v>92798</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>

--- a/artfynd/Ramsjöns naturreservat artfynd.xlsx
+++ b/artfynd/Ramsjöns naturreservat artfynd.xlsx
@@ -42100,7 +42100,7 @@
         <v>136880933</v>
       </c>
       <c r="B357" t="n">
-        <v>92747</v>
+        <v>92751</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>136881050</v>
       </c>
       <c r="B362" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>136880999</v>
       </c>
       <c r="B366" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>136881979</v>
       </c>
       <c r="B368" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
